--- a/GP_Gender_Age_Summary.xlsx
+++ b/GP_Gender_Age_Summary.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E165"/>
+  <dimension ref="A1:F312"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,20 +362,25 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Staff_Role</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Gender</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Age_Band</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Avg_FTE</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Avg_Headcount</t>
         </is>
@@ -389,19 +394,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>40-49</t>
         </is>
       </c>
-      <c r="D2">
-        <v>2147.55132651</v>
-      </c>
       <c r="E2">
-        <v>2981</v>
+        <v>1523.3679289405</v>
+      </c>
+      <c r="F2">
+        <v>1929.75</v>
       </c>
     </row>
     <row r="3">
@@ -412,19 +422,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>50-59</t>
         </is>
       </c>
-      <c r="D3">
-        <v>1600.281670635</v>
-      </c>
       <c r="E3">
-        <v>2130.75</v>
+        <v>1337.13449288125</v>
+      </c>
+      <c r="F3">
+        <v>1679.25</v>
       </c>
     </row>
     <row r="4">
@@ -435,19 +450,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>60 and over</t>
         </is>
       </c>
-      <c r="D4">
-        <v>268.3534851</v>
-      </c>
       <c r="E4">
-        <v>357.75</v>
+        <v>236.293897168</v>
+      </c>
+      <c r="F4">
+        <v>295.5</v>
       </c>
     </row>
     <row r="5">
@@ -458,19 +478,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>Under 40</t>
         </is>
       </c>
-      <c r="D5">
-        <v>1524.512048870833</v>
-      </c>
       <c r="E5">
-        <v>2105.666666666667</v>
+        <v>591.4166406485</v>
+      </c>
+      <c r="F5">
+        <v>737.5</v>
       </c>
     </row>
     <row r="6">
@@ -481,19 +506,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="D6">
-        <v>80.7005443585</v>
-      </c>
       <c r="E6">
-        <v>105</v>
+        <v>54.7588275355</v>
+      </c>
+      <c r="F6">
+        <v>65.5</v>
       </c>
     </row>
     <row r="7">
@@ -504,19 +534,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>40-49</t>
         </is>
       </c>
-      <c r="D7">
-        <v>2187.02028083575</v>
-      </c>
       <c r="E7">
-        <v>2294.5</v>
+        <v>1923.650359876</v>
+      </c>
+      <c r="F7">
+        <v>1956.25</v>
       </c>
     </row>
     <row r="8">
@@ -527,19 +562,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>50-59</t>
         </is>
       </c>
-      <c r="D8">
-        <v>2671.17551865525</v>
-      </c>
       <c r="E8">
-        <v>2800.75</v>
+        <v>2503.6248114815</v>
+      </c>
+      <c r="F8">
+        <v>2573.25</v>
       </c>
     </row>
     <row r="9">
@@ -550,19 +590,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>60 and over</t>
         </is>
       </c>
-      <c r="D9">
-        <v>870.592207011</v>
-      </c>
       <c r="E9">
-        <v>1049</v>
+        <v>805.1667091805</v>
+      </c>
+      <c r="F9">
+        <v>934.25</v>
       </c>
     </row>
     <row r="10">
@@ -573,19 +618,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>Under 40</t>
         </is>
       </c>
-      <c r="D10">
-        <v>1126.3054188165</v>
-      </c>
       <c r="E10">
-        <v>1222.333333333333</v>
+        <v>773.759358799</v>
+      </c>
+      <c r="F10">
+        <v>790.5</v>
       </c>
     </row>
     <row r="11">
@@ -596,19 +646,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="D11">
-        <v>93.5346027985</v>
-      </c>
       <c r="E11">
-        <v>105.5</v>
+        <v>73.93089105350001</v>
+      </c>
+      <c r="F11">
+        <v>78.5</v>
       </c>
     </row>
     <row r="12">
@@ -619,19 +674,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>Other/Unknown</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>40-49</t>
         </is>
       </c>
-      <c r="D12">
-        <v>1.5084709245</v>
-      </c>
       <c r="E12">
-        <v>2.25</v>
+        <v>0.862450054</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -642,18 +702,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>Other/Unknown</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>50-59</t>
         </is>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>1.9245583605</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>2.5</v>
       </c>
     </row>
@@ -665,19 +730,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>Other/Unknown</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>60 and over</t>
         </is>
       </c>
-      <c r="D14">
-        <v>1.492732797666667</v>
-      </c>
       <c r="E14">
-        <v>1.666666666666667</v>
+        <v>1.276508882333333</v>
+      </c>
+      <c r="F14">
+        <v>1.333333333333333</v>
       </c>
     </row>
     <row r="15">
@@ -688,19 +758,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>Other/Unknown</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Under 40</t>
         </is>
       </c>
-      <c r="D15">
-        <v>1.738737741</v>
-      </c>
       <c r="E15">
-        <v>2.666666666666667</v>
+        <v>0.857997059</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -711,341 +786,416 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>Other/Unknown</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="D16">
-        <v>929.854594398</v>
-      </c>
       <c r="E16">
-        <v>1167</v>
+        <v>701.0784938449999</v>
+      </c>
+      <c r="F16">
+        <v>815</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2016/17</t>
+          <t>2015/16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>40-49</t>
         </is>
       </c>
-      <c r="D17">
-        <v>2196.017235780667</v>
-      </c>
       <c r="E17">
-        <v>3047.666666666667</v>
+        <v>624.1833975695</v>
+      </c>
+      <c r="F17">
+        <v>1060</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2016/17</t>
+          <t>2015/16</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>50-59</t>
         </is>
       </c>
-      <c r="D18">
-        <v>1662.426729115667</v>
-      </c>
       <c r="E18">
-        <v>2221.333333333333</v>
+        <v>263.14717775375</v>
+      </c>
+      <c r="F18">
+        <v>458</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2016/17</t>
+          <t>2015/16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>60 and over</t>
         </is>
       </c>
-      <c r="D19">
-        <v>290.245827452</v>
-      </c>
       <c r="E19">
-        <v>390</v>
+        <v>32.059587932</v>
+      </c>
+      <c r="F19">
+        <v>62.25</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2016/17</t>
+          <t>2015/16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t>Under 40</t>
         </is>
       </c>
-      <c r="D20">
-        <v>1521.193496886</v>
-      </c>
       <c r="E20">
-        <v>2117</v>
+        <v>933.0954082223334</v>
+      </c>
+      <c r="F20">
+        <v>1373.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2016/17</t>
+          <t>2015/16</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="D21">
-        <v>83.23515904633334</v>
-      </c>
       <c r="E21">
-        <v>112</v>
+        <v>25.941716823</v>
+      </c>
+      <c r="F21">
+        <v>39.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2016/17</t>
+          <t>2015/16</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t>40-49</t>
         </is>
       </c>
-      <c r="D22">
-        <v>2207.331426818334</v>
-      </c>
       <c r="E22">
-        <v>2312.833333333333</v>
+        <v>263.36992095975</v>
+      </c>
+      <c r="F22">
+        <v>344.75</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2016/17</t>
+          <t>2015/16</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t>50-59</t>
         </is>
       </c>
-      <c r="D23">
-        <v>2630.485291399833</v>
-      </c>
       <c r="E23">
-        <v>2750.166666666667</v>
+        <v>167.55070717375</v>
+      </c>
+      <c r="F23">
+        <v>234.25</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2016/17</t>
+          <t>2015/16</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
           <t>60 and over</t>
         </is>
       </c>
-      <c r="D24">
-        <v>922.4620234266666</v>
-      </c>
       <c r="E24">
-        <v>1088</v>
+        <v>65.42549783050001</v>
+      </c>
+      <c r="F24">
+        <v>117</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2016/17</t>
+          <t>2015/16</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
           <t>Under 40</t>
         </is>
       </c>
-      <c r="D25">
-        <v>1066.429803191333</v>
-      </c>
       <c r="E25">
-        <v>1166.555555555556</v>
+        <v>352.5460600175</v>
+      </c>
+      <c r="F25">
+        <v>440</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2016/17</t>
+          <t>2015/16</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="D26">
-        <v>96.406045654</v>
-      </c>
       <c r="E26">
-        <v>106.3333333333333</v>
+        <v>19.603711745</v>
+      </c>
+      <c r="F26">
+        <v>27</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2016/17</t>
+          <t>2015/16</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
           <t>Other/Unknown</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>40-49</t>
         </is>
       </c>
-      <c r="D27">
-        <v>1.149377159</v>
-      </c>
       <c r="E27">
-        <v>1.666666666666667</v>
+        <v>1.292858411</v>
+      </c>
+      <c r="F27">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2016/17</t>
+          <t>2015/16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
           <t>Other/Unknown</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>50-59</t>
-        </is>
-      </c>
-      <c r="D28">
-        <v>0.59067969075</v>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>60 and over</t>
+        </is>
       </c>
       <c r="E28">
+        <v>0.648671746</v>
+      </c>
+      <c r="F28">
         <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2016/17</t>
+          <t>2015/16</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
           <t>Other/Unknown</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>60 and over</t>
-        </is>
-      </c>
-      <c r="D29">
-        <v>0.6463770573333333</v>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Under 40</t>
+        </is>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>1.452738721333333</v>
+      </c>
+      <c r="F29">
+        <v>2.333333333333333</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2016/17</t>
+          <t>2015/16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>Other/Unknown</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Under 40</t>
-        </is>
-      </c>
-      <c r="D30">
-        <v>1.516030798888889</v>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
       </c>
       <c r="E30">
-        <v>2.444444444444445</v>
+        <v>228.776100553</v>
+      </c>
+      <c r="F30">
+        <v>352</v>
       </c>
     </row>
     <row r="31">
@@ -1056,3101 +1206,7892 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Other/Unknown</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D31">
-        <v>520.4042491183334</v>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
       </c>
       <c r="E31">
-        <v>657.3333333333334</v>
+        <v>1508.9154272365</v>
+      </c>
+      <c r="F31">
+        <v>1906</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2017/18</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>40-49</t>
-        </is>
-      </c>
-      <c r="D32">
-        <v>2216.907735157875</v>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
       </c>
       <c r="E32">
-        <v>3116.75</v>
+        <v>1364.255579133167</v>
+      </c>
+      <c r="F32">
+        <v>1711.166666666667</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2017/18</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>50-59</t>
-        </is>
-      </c>
-      <c r="D33">
-        <v>1675.222941251625</v>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>60 and over</t>
+        </is>
       </c>
       <c r="E33">
-        <v>2271.625</v>
+        <v>251.6197055918333</v>
+      </c>
+      <c r="F33">
+        <v>313.1666666666667</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2017/18</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>60 and over</t>
-        </is>
-      </c>
-      <c r="D34">
-        <v>307.047367405</v>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Under 40</t>
+        </is>
       </c>
       <c r="E34">
-        <v>409.5</v>
+        <v>535.6033446906666</v>
+      </c>
+      <c r="F34">
+        <v>664</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2017/18</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Under 40</t>
-        </is>
-      </c>
-      <c r="D35">
-        <v>1507.353964331</v>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
       </c>
       <c r="E35">
-        <v>2110.25</v>
+        <v>50.01866071966666</v>
+      </c>
+      <c r="F35">
+        <v>58.66666666666666</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2017/18</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D36">
-        <v>89.514907658</v>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
       </c>
       <c r="E36">
-        <v>122</v>
+        <v>1912.1367157505</v>
+      </c>
+      <c r="F36">
+        <v>1933.166666666667</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2017/18</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>40-49</t>
-        </is>
-      </c>
-      <c r="D37">
-        <v>2201.22262592775</v>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
       </c>
       <c r="E37">
-        <v>2325</v>
+        <v>2450.622956914333</v>
+      </c>
+      <c r="F37">
+        <v>2505.833333333333</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2017/18</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>50-59</t>
-        </is>
-      </c>
-      <c r="D38">
-        <v>2536.7447203245</v>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>60 and over</t>
+        </is>
       </c>
       <c r="E38">
-        <v>2674.5</v>
+        <v>842.6497179603333</v>
+      </c>
+      <c r="F38">
+        <v>953.5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2017/18</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>60 and over</t>
-        </is>
-      </c>
-      <c r="D39">
-        <v>939.607609156125</v>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Under 40</t>
+        </is>
       </c>
       <c r="E39">
-        <v>1100.75</v>
+        <v>700.9087470314445</v>
+      </c>
+      <c r="F39">
+        <v>717</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2017/18</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Under 40</t>
-        </is>
-      </c>
-      <c r="D40">
-        <v>1009.558663152583</v>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
       </c>
       <c r="E40">
-        <v>1125.833333333333</v>
+        <v>74.98554533633333</v>
+      </c>
+      <c r="F40">
+        <v>77.33333333333333</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2017/18</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D41">
-        <v>90.36245952525</v>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
       </c>
       <c r="E41">
-        <v>103.25</v>
+        <v>0.8627187630000001</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2017/18</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
           <t>Other/Unknown</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>40-49</t>
-        </is>
-      </c>
-      <c r="D42">
-        <v>1.187480234166667</v>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
       </c>
       <c r="E42">
-        <v>2</v>
+        <v>0.59067969075</v>
+      </c>
+      <c r="F42">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2017/18</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
           <t>Other/Unknown</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>50-59</t>
-        </is>
-      </c>
-      <c r="D43">
-        <v>0.6165647406</v>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
       </c>
       <c r="E43">
-        <v>1.2</v>
+        <v>380.6771150396667</v>
+      </c>
+      <c r="F43">
+        <v>441.3333333333333</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2017/18</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Other/Unknown</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Under 40</t>
-        </is>
-      </c>
-      <c r="D44">
-        <v>2.597287576454546</v>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
       </c>
       <c r="E44">
-        <v>4.272727272727272</v>
+        <v>687.1018085441667</v>
+      </c>
+      <c r="F44">
+        <v>1152.5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2017/18</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Other/Unknown</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D45">
-        <v>305.52329552575</v>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
       </c>
       <c r="E45">
-        <v>386</v>
+        <v>298.1711499825</v>
+      </c>
+      <c r="F45">
+        <v>517.6666666666666</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>40-49</t>
-        </is>
-      </c>
-      <c r="D46">
-        <v>2239.44387200575</v>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>60 and over</t>
+        </is>
       </c>
       <c r="E46">
-        <v>3190.375</v>
+        <v>38.62612186016666</v>
+      </c>
+      <c r="F46">
+        <v>77.16666666666667</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>50-59</t>
-        </is>
-      </c>
-      <c r="D47">
-        <v>1681.01431179175</v>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Under 40</t>
+        </is>
       </c>
       <c r="E47">
-        <v>2280.5</v>
+        <v>985.5901521953333</v>
+      </c>
+      <c r="F47">
+        <v>1458.222222222222</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>60 and over</t>
-        </is>
-      </c>
-      <c r="D48">
-        <v>322.823661718125</v>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
       </c>
       <c r="E48">
-        <v>427</v>
+        <v>33.21649832666667</v>
+      </c>
+      <c r="F48">
+        <v>53.33333333333334</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Under 40</t>
-        </is>
-      </c>
-      <c r="D49">
-        <v>1495.181676384417</v>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
       </c>
       <c r="E49">
-        <v>2131.5</v>
+        <v>295.1947110678333</v>
+      </c>
+      <c r="F49">
+        <v>386.6666666666667</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D50">
-        <v>61.57438110475</v>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
       </c>
       <c r="E50">
-        <v>94.25</v>
+        <v>179.8623344855</v>
+      </c>
+      <c r="F50">
+        <v>253.3333333333333</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>40-49</t>
-        </is>
-      </c>
-      <c r="D51">
-        <v>2184.988071809875</v>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>60 and over</t>
+        </is>
       </c>
       <c r="E51">
-        <v>2326.25</v>
+        <v>79.81230546633333</v>
+      </c>
+      <c r="F51">
+        <v>136.3333333333333</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>50-59</t>
-        </is>
-      </c>
-      <c r="D52">
-        <v>2401.12240419525</v>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Under 40</t>
+        </is>
       </c>
       <c r="E52">
-        <v>2530.75</v>
+        <v>365.5210561598889</v>
+      </c>
+      <c r="F52">
+        <v>457.8888888888889</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>60 and over</t>
-        </is>
-      </c>
-      <c r="D53">
-        <v>946.7187140748749</v>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
       </c>
       <c r="E53">
-        <v>1112.75</v>
+        <v>21.42050031766667</v>
+      </c>
+      <c r="F53">
+        <v>29</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Under 40</t>
-        </is>
-      </c>
-      <c r="D54">
-        <v>934.8536902009166</v>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
       </c>
       <c r="E54">
-        <v>1081.833333333333</v>
+        <v>0.8618042379999999</v>
+      </c>
+      <c r="F54">
+        <v>1.333333333333333</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D55">
-        <v>54.97911483425</v>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>60 and over</t>
+        </is>
       </c>
       <c r="E55">
-        <v>68.5</v>
+        <v>0.6463770573333333</v>
+      </c>
+      <c r="F55">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
           <t>Other/Unknown</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>40-49</t>
-        </is>
-      </c>
-      <c r="D56">
-        <v>5.4348768475</v>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Under 40</t>
+        </is>
       </c>
       <c r="E56">
-        <v>8.5</v>
+        <v>1.516030798888889</v>
+      </c>
+      <c r="F56">
+        <v>2.444444444444445</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2016/17</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
           <t>Other/Unknown</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>50-59</t>
-        </is>
-      </c>
-      <c r="D57">
-        <v>4.97717676275</v>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
       </c>
       <c r="E57">
-        <v>6.75</v>
+        <v>139.7271340786667</v>
+      </c>
+      <c r="F57">
+        <v>216</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2017/18</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Other/Unknown</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>60 and over</t>
-        </is>
-      </c>
-      <c r="D58">
-        <v>2.8666666665</v>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
       </c>
       <c r="E58">
-        <v>3.5</v>
+        <v>1475.031142474875</v>
+      </c>
+      <c r="F58">
+        <v>1883.125</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2017/18</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Other/Unknown</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Under 40</t>
-        </is>
-      </c>
-      <c r="D59">
-        <v>9.173746969666666</v>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
       </c>
       <c r="E59">
-        <v>12.91666666666667</v>
+        <v>1355.447765298375</v>
+      </c>
+      <c r="F59">
+        <v>1722.875</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2018/19</t>
+          <t>2017/18</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Other/Unknown</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D60">
-        <v>367.106308137</v>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>60 and over</t>
+        </is>
       </c>
       <c r="E60">
-        <v>466.75</v>
+        <v>262.124388274625</v>
+      </c>
+      <c r="F60">
+        <v>323.875</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2017/18</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>40-49</t>
-        </is>
-      </c>
-      <c r="D61">
-        <v>2287.830295115875</v>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Under 40</t>
+        </is>
       </c>
       <c r="E61">
-        <v>3309.25</v>
+        <v>497.9976238705833</v>
+      </c>
+      <c r="F61">
+        <v>623.6666666666666</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2017/18</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>50-59</t>
-        </is>
-      </c>
-      <c r="D62">
-        <v>1673.05096134075</v>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
       </c>
       <c r="E62">
-        <v>2292.25</v>
+        <v>51.8730977175</v>
+      </c>
+      <c r="F62">
+        <v>61.5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2017/18</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>60 and over</t>
-        </is>
-      </c>
-      <c r="D63">
-        <v>323.542551330625</v>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
       </c>
       <c r="E63">
-        <v>437.125</v>
+        <v>1897.092430861625</v>
+      </c>
+      <c r="F63">
+        <v>1932.375</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2017/18</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Under 40</t>
-        </is>
-      </c>
-      <c r="D64">
-        <v>1505.736075132917</v>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
       </c>
       <c r="E64">
-        <v>2190.083333333333</v>
+        <v>2349.2440749945</v>
+      </c>
+      <c r="F64">
+        <v>2422</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2017/18</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D65">
-        <v>37.66158220175</v>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>60 and over</t>
+        </is>
       </c>
       <c r="E65">
-        <v>55</v>
+        <v>858.210806158</v>
+      </c>
+      <c r="F65">
+        <v>965.5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2017/18</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>40-49</t>
-        </is>
-      </c>
-      <c r="D66">
-        <v>2158.59379486225</v>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Under 40</t>
+        </is>
       </c>
       <c r="E66">
-        <v>2334.75</v>
+        <v>626.3145328475833</v>
+      </c>
+      <c r="F66">
+        <v>647.8333333333334</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2017/18</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>50-59</t>
-        </is>
-      </c>
-      <c r="D67">
-        <v>2247.486508508875</v>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
       </c>
       <c r="E67">
-        <v>2401.5</v>
+        <v>68.6659198175</v>
+      </c>
+      <c r="F67">
+        <v>71</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2017/18</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>60 and over</t>
-        </is>
-      </c>
-      <c r="D68">
-        <v>938.1788716667501</v>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
       </c>
       <c r="E68">
-        <v>1104.125</v>
+        <v>0.856663022</v>
+      </c>
+      <c r="F68">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2017/18</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Under 40</t>
-        </is>
-      </c>
-      <c r="D69">
-        <v>907.5216562868334</v>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
       </c>
       <c r="E69">
-        <v>1087.416666666667</v>
+        <v>0.5</v>
+      </c>
+      <c r="F69">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2017/18</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D70">
-        <v>42.26541057525</v>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Under 40</t>
+        </is>
       </c>
       <c r="E70">
-        <v>51</v>
+        <v>0.8548864309999999</v>
+      </c>
+      <c r="F70">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2017/18</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
           <t>Other/Unknown</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>40-49</t>
-        </is>
-      </c>
-      <c r="D71">
-        <v>1.381999999625</v>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
       </c>
       <c r="E71">
-        <v>2.25</v>
+        <v>221.29564549075</v>
+      </c>
+      <c r="F71">
+        <v>254.5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2017/18</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Other/Unknown</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>50-59</t>
-        </is>
-      </c>
-      <c r="D72">
-        <v>0.987715266125</v>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
       </c>
       <c r="E72">
-        <v>2</v>
+        <v>741.876592683</v>
+      </c>
+      <c r="F72">
+        <v>1251</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2017/18</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Other/Unknown</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>60 and over</t>
-        </is>
-      </c>
-      <c r="D73">
-        <v>1</v>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
       </c>
       <c r="E73">
-        <v>1</v>
+        <v>319.77517595325</v>
+      </c>
+      <c r="F73">
+        <v>558.5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2017/18</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Other/Unknown</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Under 40</t>
-        </is>
-      </c>
-      <c r="D74">
-        <v>2.458818673636364</v>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>60 and over</t>
+        </is>
       </c>
       <c r="E74">
-        <v>3.454545454545455</v>
+        <v>44.922979130375</v>
+      </c>
+      <c r="F74">
+        <v>86.75</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2019/20</t>
+          <t>2017/18</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Other/Unknown</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D75">
-        <v>313.37149293125</v>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Under 40</t>
+        </is>
       </c>
       <c r="E75">
-        <v>401.75</v>
+        <v>1009.356340460417</v>
+      </c>
+      <c r="F75">
+        <v>1495.083333333333</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2017/18</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>40-49</t>
-        </is>
-      </c>
-      <c r="D76">
-        <v>2352.241643680375</v>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
       </c>
       <c r="E76">
-        <v>3458.5</v>
+        <v>37.6418099405</v>
+      </c>
+      <c r="F76">
+        <v>60.5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2017/18</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>50-59</t>
-        </is>
-      </c>
-      <c r="D77">
-        <v>1665.678760961125</v>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
       </c>
       <c r="E77">
-        <v>2310.375</v>
+        <v>304.130195066125</v>
+      </c>
+      <c r="F77">
+        <v>401.875</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2017/18</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>60 and over</t>
-        </is>
-      </c>
-      <c r="D78">
-        <v>338.536441340375</v>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
       </c>
       <c r="E78">
-        <v>469.5</v>
+        <v>187.50064533</v>
+      </c>
+      <c r="F78">
+        <v>262.375</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2017/18</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Under 40</t>
-        </is>
-      </c>
-      <c r="D79">
-        <v>1534.387764896417</v>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>60 and over</t>
+        </is>
       </c>
       <c r="E79">
-        <v>2269.583333333333</v>
+        <v>81.396802998125</v>
+      </c>
+      <c r="F79">
+        <v>139</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2017/18</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D80">
-        <v>26.221384901</v>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Under 40</t>
+        </is>
       </c>
       <c r="E80">
-        <v>37.75</v>
+        <v>383.244130305</v>
+      </c>
+      <c r="F80">
+        <v>487.9166666666667</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2017/18</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>40-49</t>
-        </is>
-      </c>
-      <c r="D81">
-        <v>2158.89882007725</v>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
       </c>
       <c r="E81">
-        <v>2380.625</v>
+        <v>21.69653970775</v>
+      </c>
+      <c r="F81">
+        <v>32.25</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2017/18</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>50-59</t>
-        </is>
-      </c>
-      <c r="D82">
-        <v>2111.237998405625</v>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
       </c>
       <c r="E82">
-        <v>2280.75</v>
+        <v>1.044703063833333</v>
+      </c>
+      <c r="F82">
+        <v>1.833333333333333</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2017/18</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>60 and over</t>
-        </is>
-      </c>
-      <c r="D83">
-        <v>946.87510270325</v>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
       </c>
       <c r="E83">
-        <v>1113.25</v>
+        <v>0.5414118514999999</v>
+      </c>
+      <c r="F83">
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2017/18</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
           <t>Under 40</t>
         </is>
       </c>
-      <c r="D84">
-        <v>894.7709799318334</v>
-      </c>
       <c r="E84">
-        <v>1115.666666666667</v>
+        <v>2.519570628181818</v>
+      </c>
+      <c r="F84">
+        <v>4.181818181818182</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2017/18</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="D85">
-        <v>36.19529934725</v>
-      </c>
       <c r="E85">
-        <v>41.5</v>
+        <v>84.227650035</v>
+      </c>
+      <c r="F85">
+        <v>131.5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Other/Unknown</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
           <t>40-49</t>
         </is>
       </c>
-      <c r="D86">
-        <v>2.367163909</v>
-      </c>
       <c r="E86">
-        <v>3.75</v>
+        <v>1442.578281506375</v>
+      </c>
+      <c r="F86">
+        <v>1851.75</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Other/Unknown</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
           <t>50-59</t>
         </is>
       </c>
-      <c r="D87">
-        <v>0.87166666675</v>
-      </c>
       <c r="E87">
-        <v>2</v>
+        <v>1331.822726301</v>
+      </c>
+      <c r="F87">
+        <v>1689.25</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Other/Unknown</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
           <t>60 and over</t>
         </is>
       </c>
-      <c r="D88">
-        <v>1.7421174645</v>
-      </c>
       <c r="E88">
-        <v>2.75</v>
+        <v>266.153221712625</v>
+      </c>
+      <c r="F88">
+        <v>326.625</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Other/Unknown</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
           <t>Under 40</t>
         </is>
       </c>
-      <c r="D89">
-        <v>3.665810691818182</v>
-      </c>
       <c r="E89">
-        <v>5</v>
+        <v>448.2429130259167</v>
+      </c>
+      <c r="F89">
+        <v>567.1666666666666</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2020/21</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Other/Unknown</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="D90">
-        <v>225.21523336025</v>
-      </c>
       <c r="E90">
-        <v>293</v>
+        <v>25.72942315375</v>
+      </c>
+      <c r="F90">
+        <v>32.75</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
           <t>40-49</t>
         </is>
       </c>
-      <c r="D91">
-        <v>2412.8553623241</v>
-      </c>
       <c r="E91">
-        <v>3569.55</v>
+        <v>1861.090996698125</v>
+      </c>
+      <c r="F91">
+        <v>1903.625</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
           <t>50-59</t>
         </is>
       </c>
-      <c r="D92">
-        <v>1690.6770674608</v>
-      </c>
       <c r="E92">
-        <v>2359.5</v>
+        <v>2197.1363164495</v>
+      </c>
+      <c r="F92">
+        <v>2256.125</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
           <t>60 and over</t>
         </is>
       </c>
-      <c r="D93">
-        <v>361.54603274605</v>
-      </c>
       <c r="E93">
-        <v>504.8</v>
+        <v>855.92632839675</v>
+      </c>
+      <c r="F93">
+        <v>960.875</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
           <t>Under 40</t>
         </is>
       </c>
-      <c r="D94">
-        <v>1537.098523466833</v>
-      </c>
       <c r="E94">
-        <v>2273.766666666667</v>
+        <v>548.8391394376666</v>
+      </c>
+      <c r="F94">
+        <v>582.25</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="D95">
-        <v>68.6327129921</v>
-      </c>
       <c r="E95">
-        <v>109.5</v>
+        <v>36.6426930505</v>
+      </c>
+      <c r="F95">
+        <v>40.25</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
           <t>40-49</t>
         </is>
       </c>
-      <c r="D96">
-        <v>2136.73137445965</v>
-      </c>
       <c r="E96">
-        <v>2382.25</v>
+        <v>4.1055284515</v>
+      </c>
+      <c r="F96">
+        <v>5.75</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
           <t>50-59</t>
         </is>
       </c>
-      <c r="D97">
-        <v>2025.9153790173</v>
-      </c>
       <c r="E97">
-        <v>2217.7</v>
+        <v>3.760037832428571</v>
+      </c>
+      <c r="F97">
+        <v>4.571428571428571</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
           <t>60 and over</t>
         </is>
       </c>
-      <c r="D98">
-        <v>941.9646385863</v>
-      </c>
       <c r="E98">
-        <v>1119.85</v>
+        <v>2.2133333335</v>
+      </c>
+      <c r="F98">
+        <v>2.5</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
           <t>Under 40</t>
         </is>
       </c>
-      <c r="D99">
-        <v>885.5672806532333</v>
-      </c>
       <c r="E99">
-        <v>1121.766666666667</v>
+        <v>4.057523632333333</v>
+      </c>
+      <c r="F99">
+        <v>4.5</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="D100">
-        <v>58.2480214847</v>
-      </c>
       <c r="E100">
-        <v>78.8</v>
+        <v>260.4850015035</v>
+      </c>
+      <c r="F100">
+        <v>302</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Other/Unknown</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
           <t>40-49</t>
         </is>
       </c>
-      <c r="D101">
-        <v>2.7058759165</v>
-      </c>
       <c r="E101">
-        <v>4</v>
+        <v>796.865590499375</v>
+      </c>
+      <c r="F101">
+        <v>1357.125</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Other/Unknown</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
           <t>50-59</t>
         </is>
       </c>
-      <c r="D102">
-        <v>1.524866666625</v>
-      </c>
       <c r="E102">
-        <v>2.75</v>
+        <v>349.19158549075</v>
+      </c>
+      <c r="F102">
+        <v>602.125</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Other/Unknown</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
           <t>60 and over</t>
         </is>
       </c>
-      <c r="D103">
-        <v>1.8786922651</v>
-      </c>
       <c r="E103">
-        <v>3.1</v>
+        <v>56.67044000550001</v>
+      </c>
+      <c r="F103">
+        <v>101.75</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Other/Unknown</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
           <t>Under 40</t>
         </is>
       </c>
-      <c r="D104">
-        <v>4.298662908047619</v>
-      </c>
       <c r="E104">
-        <v>6.095238095238095</v>
+        <v>1046.9387633585</v>
+      </c>
+      <c r="F104">
+        <v>1571.5</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2021/22</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Other/Unknown</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="D105">
-        <v>208.5956382907</v>
-      </c>
       <c r="E105">
-        <v>277.2</v>
+        <v>35.844957951</v>
+      </c>
+      <c r="F105">
+        <v>61.5</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
           <t>40-49</t>
         </is>
       </c>
-      <c r="D106">
-        <v>2462.934821838292</v>
-      </c>
       <c r="E106">
-        <v>3633.541666666667</v>
+        <v>323.89707511175</v>
+      </c>
+      <c r="F106">
+        <v>433</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
           <t>50-59</t>
         </is>
       </c>
-      <c r="D107">
-        <v>1702.9881152235</v>
-      </c>
       <c r="E107">
-        <v>2376.5</v>
+        <v>203.98608774575</v>
+      </c>
+      <c r="F107">
+        <v>283.375</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
           <t>60 and over</t>
         </is>
       </c>
-      <c r="D108">
-        <v>384.1701661614583</v>
-      </c>
       <c r="E108">
-        <v>533.1666666666666</v>
+        <v>90.792385678125</v>
+      </c>
+      <c r="F108">
+        <v>156.25</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
           <t>Under 40</t>
         </is>
       </c>
-      <c r="D109">
-        <v>1491.660384711111</v>
-      </c>
       <c r="E109">
-        <v>2202.388888888889</v>
+        <v>386.01455076325</v>
+      </c>
+      <c r="F109">
+        <v>507.5833333333333</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="D110">
-        <v>52.52970153525</v>
-      </c>
       <c r="E110">
-        <v>85.5</v>
+        <v>18.33642178375</v>
+      </c>
+      <c r="F110">
+        <v>28.25</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
           <t>40-49</t>
         </is>
       </c>
-      <c r="D111">
-        <v>2105.307745192</v>
-      </c>
       <c r="E111">
-        <v>2364.375</v>
+        <v>3.38211262175</v>
+      </c>
+      <c r="F111">
+        <v>5.625</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
           <t>50-59</t>
         </is>
       </c>
-      <c r="D112">
-        <v>1959.663236869708</v>
-      </c>
       <c r="E112">
-        <v>2154.75</v>
+        <v>1.687143659375</v>
+      </c>
+      <c r="F112">
+        <v>2.75</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
           <t>60 and over</t>
         </is>
       </c>
-      <c r="D113">
-        <v>939.0237908830001</v>
-      </c>
       <c r="E113">
-        <v>1128.875</v>
+        <v>0.653333333</v>
+      </c>
+      <c r="F113">
+        <v>1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
           <t>Under 40</t>
         </is>
       </c>
-      <c r="D114">
-        <v>870.8027582629167</v>
-      </c>
       <c r="E114">
-        <v>1107</v>
+        <v>7.1449851535</v>
+      </c>
+      <c r="F114">
+        <v>10.66666666666667</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2018/19</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="D115">
-        <v>47.06066895958333</v>
-      </c>
       <c r="E115">
-        <v>61.83333333333334</v>
+        <v>106.6213066335</v>
+      </c>
+      <c r="F115">
+        <v>164.75</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Other/Unknown</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
           <t>40-49</t>
         </is>
       </c>
-      <c r="D116">
-        <v>2.890434783130435</v>
-      </c>
       <c r="E116">
-        <v>4.173913043478261</v>
+        <v>1432.169248799</v>
+      </c>
+      <c r="F116">
+        <v>1856.875</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Other/Unknown</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
           <t>50-59</t>
         </is>
       </c>
-      <c r="D117">
-        <v>1.340150724391304</v>
-      </c>
       <c r="E117">
-        <v>2.304347826086957</v>
+        <v>1297.56760926075</v>
+      </c>
+      <c r="F117">
+        <v>1649.625</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Other/Unknown</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
           <t>60 and over</t>
         </is>
       </c>
-      <c r="D118">
-        <v>1.86</v>
-      </c>
       <c r="E118">
-        <v>3</v>
+        <v>254.918968602125</v>
+      </c>
+      <c r="F118">
+        <v>313.375</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Other/Unknown</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
           <t>Under 40</t>
         </is>
       </c>
-      <c r="D119">
-        <v>2.838274511958333</v>
-      </c>
       <c r="E119">
-        <v>4.041666666666667</v>
+        <v>423.3973953975834</v>
+      </c>
+      <c r="F119">
+        <v>540.6666666666666</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2022/23</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Other/Unknown</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="D120">
-        <v>223.8026259659167</v>
-      </c>
       <c r="E120">
-        <v>301.25</v>
+        <v>15.77999999975</v>
+      </c>
+      <c r="F120">
+        <v>19.5</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2023/24</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
           <t>40-49</t>
         </is>
       </c>
-      <c r="D121">
-        <v>2507.008297121208</v>
-      </c>
       <c r="E121">
-        <v>3718.833333333333</v>
+        <v>1826.19483599475</v>
+      </c>
+      <c r="F121">
+        <v>1891.5</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2023/24</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
           <t>50-59</t>
         </is>
       </c>
-      <c r="D122">
-        <v>1736.477333452</v>
-      </c>
       <c r="E122">
-        <v>2424.083333333333</v>
+        <v>2030.833449271125</v>
+      </c>
+      <c r="F122">
+        <v>2100.875</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2023/24</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
           <t>60 and over</t>
         </is>
       </c>
-      <c r="D123">
-        <v>412.9504976349166</v>
-      </c>
       <c r="E123">
-        <v>575</v>
+        <v>833.3249122726249</v>
+      </c>
+      <c r="F123">
+        <v>931.75</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2023/24</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
           <t>Under 40</t>
         </is>
       </c>
-      <c r="D124">
-        <v>1454.513750072528</v>
-      </c>
       <c r="E124">
-        <v>2171.027777777778</v>
+        <v>494.5223298621667</v>
+      </c>
+      <c r="F124">
+        <v>538.4166666666666</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2023/24</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="D125">
-        <v>47.76110655691667</v>
-      </c>
       <c r="E125">
-        <v>76.16666666666667</v>
+        <v>29.71007723925</v>
+      </c>
+      <c r="F125">
+        <v>32.5</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2023/24</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
           <t>40-49</t>
         </is>
       </c>
-      <c r="D126">
-        <v>2056.11859265125</v>
-      </c>
       <c r="E126">
-        <v>2345.708333333333</v>
+        <v>0.533333333</v>
+      </c>
+      <c r="F126">
+        <v>1</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2023/24</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
           <t>50-59</t>
         </is>
       </c>
-      <c r="D127">
-        <v>1902.941607567583</v>
-      </c>
       <c r="E127">
-        <v>2099</v>
+        <v>0.66209719925</v>
+      </c>
+      <c r="F127">
+        <v>1</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2023/24</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>60 and over</t>
-        </is>
-      </c>
-      <c r="D128">
-        <v>945.8233599653749</v>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Under 40</t>
+        </is>
       </c>
       <c r="E128">
-        <v>1132.208333333333</v>
+        <v>0.8</v>
+      </c>
+      <c r="F128">
+        <v>1</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2023/24</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Under 40</t>
-        </is>
-      </c>
-      <c r="D129">
-        <v>876.80825119975</v>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
       </c>
       <c r="E129">
-        <v>1129.194444444444</v>
+        <v>221.2351755915</v>
+      </c>
+      <c r="F129">
+        <v>258</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2023/24</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D130">
-        <v>41.34028987108334</v>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
       </c>
       <c r="E130">
-        <v>55.16666666666666</v>
+        <v>855.6610463168749</v>
+      </c>
+      <c r="F130">
+        <v>1466.75</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2023/24</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Other/Unknown</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>40-49</t>
-        </is>
-      </c>
-      <c r="D131">
-        <v>2.123333333833334</v>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
       </c>
       <c r="E131">
-        <v>3.041666666666667</v>
+        <v>375.48335208</v>
+      </c>
+      <c r="F131">
+        <v>650.75</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2023/24</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Other/Unknown</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>50-59</t>
-        </is>
-      </c>
-      <c r="D132">
-        <v>1.147847618714286</v>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>60 and over</t>
+        </is>
       </c>
       <c r="E132">
-        <v>2.380952380952381</v>
+        <v>68.6235827285</v>
+      </c>
+      <c r="F132">
+        <v>124.5</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2023/24</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Other/Unknown</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>60 and over</t>
-        </is>
-      </c>
-      <c r="D133">
-        <v>1.690769230846154</v>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Under 40</t>
+        </is>
       </c>
       <c r="E133">
-        <v>2.538461538461538</v>
+        <v>1082.338679735333</v>
+      </c>
+      <c r="F133">
+        <v>1653.916666666667</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2023/24</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Other/Unknown</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Under 40</t>
-        </is>
-      </c>
-      <c r="D134">
-        <v>1.7433376005</v>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
       </c>
       <c r="E134">
-        <v>2.708333333333333</v>
+        <v>21.881582202</v>
+      </c>
+      <c r="F134">
+        <v>35.5</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2023/24</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Other/Unknown</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D135">
-        <v>227.54079434075</v>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
       </c>
       <c r="E135">
-        <v>308.9166666666667</v>
+        <v>332.3989588675</v>
+      </c>
+      <c r="F135">
+        <v>451.875</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>40-49</t>
-        </is>
-      </c>
-      <c r="D136">
-        <v>2596.131889173917</v>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
       </c>
       <c r="E136">
-        <v>3924.208333333333</v>
+        <v>216.65305923775</v>
+      </c>
+      <c r="F136">
+        <v>307.875</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>50-59</t>
-        </is>
-      </c>
-      <c r="D137">
-        <v>1813.696015514167</v>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>60 and over</t>
+        </is>
       </c>
       <c r="E137">
-        <v>2547.875</v>
+        <v>104.853959394125</v>
+      </c>
+      <c r="F137">
+        <v>174.25</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>60 and over</t>
-        </is>
-      </c>
-      <c r="D138">
-        <v>452.2310209324584</v>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Under 40</t>
+        </is>
       </c>
       <c r="E138">
-        <v>635.5</v>
+        <v>412.9993264246667</v>
+      </c>
+      <c r="F138">
+        <v>554.9166666666666</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Under 40</t>
-        </is>
-      </c>
-      <c r="D139">
-        <v>1465.433987776694</v>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
       </c>
       <c r="E139">
-        <v>2229.472222222222</v>
+        <v>12.555333336</v>
+      </c>
+      <c r="F139">
+        <v>18.5</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D140">
-        <v>41.47573631533334</v>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
       </c>
       <c r="E140">
-        <v>66.41666666666667</v>
+        <v>1.115333333125</v>
+      </c>
+      <c r="F140">
+        <v>1.75</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>40-49</t>
-        </is>
-      </c>
-      <c r="D141">
-        <v>2054.898557005667</v>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
       </c>
       <c r="E141">
-        <v>2390.833333333333</v>
+        <v>0.6566666665000001</v>
+      </c>
+      <c r="F141">
+        <v>1.5</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>50-59</t>
-        </is>
-      </c>
-      <c r="D142">
-        <v>1882.422434406792</v>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>60 and over</t>
+        </is>
       </c>
       <c r="E142">
-        <v>2091.375</v>
+        <v>1</v>
+      </c>
+      <c r="F142">
+        <v>1</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>60 and over</t>
-        </is>
-      </c>
-      <c r="D143">
-        <v>979.453637606625</v>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Under 40</t>
+        </is>
       </c>
       <c r="E143">
-        <v>1167</v>
+        <v>2.167909582727273</v>
+      </c>
+      <c r="F143">
+        <v>3.090909090909091</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2019/20</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Under 40</t>
-        </is>
-      </c>
-      <c r="D144">
-        <v>937.7071640074445</v>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
       </c>
       <c r="E144">
-        <v>1245.083333333333</v>
+        <v>92.13631733975001</v>
+      </c>
+      <c r="F144">
+        <v>143.75</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D145">
-        <v>37.96690320766667</v>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
       </c>
       <c r="E145">
-        <v>49.91666666666666</v>
+        <v>1415.14051288875</v>
+      </c>
+      <c r="F145">
+        <v>1854.625</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Other/Unknown</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>40-49</t>
-        </is>
-      </c>
-      <c r="D146">
-        <v>1.866666667</v>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
       </c>
       <c r="E146">
-        <v>2.5</v>
+        <v>1251.028283027125</v>
+      </c>
+      <c r="F146">
+        <v>1597.25</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Other/Unknown</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>50-59</t>
-        </is>
-      </c>
-      <c r="D147">
-        <v>0.533333333</v>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>60 and over</t>
+        </is>
       </c>
       <c r="E147">
-        <v>2</v>
+        <v>261.943851037875</v>
+      </c>
+      <c r="F147">
+        <v>325.5</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Other/Unknown</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>60 and over</t>
-        </is>
-      </c>
-      <c r="D148">
-        <v>0.9805128205384616</v>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Under 40</t>
+        </is>
       </c>
       <c r="E148">
-        <v>1</v>
+        <v>386.2194757379166</v>
+      </c>
+      <c r="F148">
+        <v>500.0833333333333</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Other/Unknown</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Under 40</t>
-        </is>
-      </c>
-      <c r="D149">
-        <v>1.075834532041667</v>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
       </c>
       <c r="E149">
-        <v>2.166666666666667</v>
+        <v>13.286666666</v>
+      </c>
+      <c r="F149">
+        <v>16.5</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Other/Unknown</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D150">
-        <v>211.0208782526667</v>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
       </c>
       <c r="E150">
-        <v>289.9166666666667</v>
+        <v>1793.2638885045</v>
+      </c>
+      <c r="F150">
+        <v>1885.125</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>40-49</t>
-        </is>
-      </c>
-      <c r="D151">
-        <v>2717.35983198445</v>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
       </c>
       <c r="E151">
-        <v>4164.6</v>
+        <v>1877.58252493</v>
+      </c>
+      <c r="F151">
+        <v>1950</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>50-59</t>
-        </is>
-      </c>
-      <c r="D152">
-        <v>1862.035413846115</v>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>60 and over</t>
+        </is>
       </c>
       <c r="E152">
-        <v>2654.2</v>
+        <v>831.9214150605001</v>
+      </c>
+      <c r="F152">
+        <v>926</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>60 and over</t>
-        </is>
-      </c>
-      <c r="D153">
-        <v>486.910815641965</v>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Under 40</t>
+        </is>
       </c>
       <c r="E153">
-        <v>686.45</v>
+        <v>440.6510322075833</v>
+      </c>
+      <c r="F153">
+        <v>491.3333333333333</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Under 40</t>
-        </is>
-      </c>
-      <c r="D154">
-        <v>1464.291476434037</v>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
       </c>
       <c r="E154">
-        <v>2255.333333333333</v>
+        <v>28.1519660125</v>
+      </c>
+      <c r="F154">
+        <v>31</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D155">
-        <v>34.24692378453</v>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
       </c>
       <c r="E155">
-        <v>52.1</v>
+        <v>0.87223057575</v>
+      </c>
+      <c r="F155">
+        <v>1.125</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>40-49</t>
-        </is>
-      </c>
-      <c r="D156">
-        <v>2073.356048551295</v>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
       </c>
       <c r="E156">
-        <v>2450.85</v>
+        <v>0.3244444446666667</v>
+      </c>
+      <c r="F156">
+        <v>1</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>50-59</t>
-        </is>
-      </c>
-      <c r="D157">
-        <v>1876.68182975322</v>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Under 40</t>
+        </is>
       </c>
       <c r="E157">
-        <v>2098.2</v>
+        <v>1.86</v>
+      </c>
+      <c r="F157">
+        <v>2.25</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>GP Partners</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>60 and over</t>
-        </is>
-      </c>
-      <c r="D158">
-        <v>990.1581128763499</v>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
       </c>
       <c r="E158">
-        <v>1181.15</v>
+        <v>151.56225010975</v>
+      </c>
+      <c r="F158">
+        <v>177</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Under 40</t>
-        </is>
-      </c>
-      <c r="D159">
-        <v>983.67416512632</v>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
       </c>
       <c r="E159">
-        <v>1330.966666666667</v>
+        <v>937.101130791625</v>
+      </c>
+      <c r="F159">
+        <v>1619.375</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D160">
-        <v>33.46664180546</v>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
       </c>
       <c r="E160">
-        <v>45</v>
+        <v>414.650477934</v>
+      </c>
+      <c r="F160">
+        <v>720.625</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Other/Unknown</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>40-49</t>
-        </is>
-      </c>
-      <c r="D161">
-        <v>1.717894737047369</v>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>60 and over</t>
+        </is>
       </c>
       <c r="E161">
-        <v>2.263157894736842</v>
+        <v>76.5925903025</v>
+      </c>
+      <c r="F161">
+        <v>144</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Other/Unknown</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>50-59</t>
-        </is>
-      </c>
-      <c r="D162">
-        <v>0.40533333323</v>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Under 40</t>
+        </is>
       </c>
       <c r="E162">
-        <v>1.4</v>
+        <v>1148.1682891585</v>
+      </c>
+      <c r="F162">
+        <v>1774.5</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Other/Unknown</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>60 and over</t>
-        </is>
-      </c>
-      <c r="D163">
-        <v>1</v>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
       </c>
       <c r="E163">
-        <v>1</v>
+        <v>12.934718235</v>
+      </c>
+      <c r="F163">
+        <v>21.25</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2020/21</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Other/Unknown</t>
+          <t>Salaried GPs</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Under 40</t>
-        </is>
-      </c>
-      <c r="D164">
-        <v>0.6865533688518518</v>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
       </c>
       <c r="E164">
-        <v>1.518518518518519</v>
+        <v>365.63493157275</v>
+      </c>
+      <c r="F164">
+        <v>503</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
+          <t>2020/21</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
+      </c>
+      <c r="E165">
+        <v>233.655473475625</v>
+      </c>
+      <c r="F165">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2020/21</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>60 and over</t>
+        </is>
+      </c>
+      <c r="E166">
+        <v>114.95368764275</v>
+      </c>
+      <c r="F166">
+        <v>189.25</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2020/21</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Under 40</t>
+        </is>
+      </c>
+      <c r="E167">
+        <v>454.11994772425</v>
+      </c>
+      <c r="F167">
+        <v>630.1666666666666</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2020/21</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E168">
+        <v>8.043333334750001</v>
+      </c>
+      <c r="F168">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2020/21</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
+      </c>
+      <c r="E169">
+        <v>1.49493333325</v>
+      </c>
+      <c r="F169">
+        <v>2.625</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2020/21</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
+      </c>
+      <c r="E170">
+        <v>0.62833333325</v>
+      </c>
+      <c r="F170">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2020/21</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>60 and over</t>
+        </is>
+      </c>
+      <c r="E171">
+        <v>1.7421174645</v>
+      </c>
+      <c r="F171">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2020/21</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Under 40</t>
+        </is>
+      </c>
+      <c r="E172">
+        <v>2.989447055454546</v>
+      </c>
+      <c r="F172">
+        <v>4.181818181818182</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2020/21</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E173">
+        <v>73.6529832505</v>
+      </c>
+      <c r="F173">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2021/22</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
+      </c>
+      <c r="E174">
+        <v>1402.6494778746</v>
+      </c>
+      <c r="F174">
+        <v>1853.25</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2021/22</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
+      </c>
+      <c r="E175">
+        <v>1240.7745705774</v>
+      </c>
+      <c r="F175">
+        <v>1583.4</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2021/22</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>60 and over</t>
+        </is>
+      </c>
+      <c r="E176">
+        <v>272.3668122263</v>
+      </c>
+      <c r="F176">
+        <v>338.85</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2021/22</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Under 40</t>
+        </is>
+      </c>
+      <c r="E177">
+        <v>359.8124541909667</v>
+      </c>
+      <c r="F177">
+        <v>466.6666666666667</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2021/22</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E178">
+        <v>16.6764025722</v>
+      </c>
+      <c r="F178">
+        <v>22.3</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2021/22</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
+      </c>
+      <c r="E179">
+        <v>1751.60647965085</v>
+      </c>
+      <c r="F179">
+        <v>1855.75</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2021/22</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
+      </c>
+      <c r="E180">
+        <v>1776.60586192805</v>
+      </c>
+      <c r="F180">
+        <v>1858.85</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2021/22</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>60 and over</t>
+        </is>
+      </c>
+      <c r="E181">
+        <v>820.30264010905</v>
+      </c>
+      <c r="F181">
+        <v>921.3</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2021/22</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Under 40</t>
+        </is>
+      </c>
+      <c r="E182">
+        <v>407.5921268039</v>
+      </c>
+      <c r="F182">
+        <v>462.8666666666667</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2021/22</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E183">
+        <v>25.445335051</v>
+      </c>
+      <c r="F183">
+        <v>31.7</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2021/22</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
+      </c>
+      <c r="E184">
+        <v>2.5066666669</v>
+      </c>
+      <c r="F184">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2021/22</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
+      </c>
+      <c r="E185">
+        <v>0.515000000125</v>
+      </c>
+      <c r="F185">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2021/22</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Under 40</t>
+        </is>
+      </c>
+      <c r="E186">
+        <v>0.793333333625</v>
+      </c>
+      <c r="F186">
+        <v>1.125</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2021/22</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E187">
+        <v>135.7678127344</v>
+      </c>
+      <c r="F187">
+        <v>160.5</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2021/22</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
+      </c>
+      <c r="E188">
+        <v>1010.2058844495</v>
+      </c>
+      <c r="F188">
+        <v>1735.9</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2021/22</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
+      </c>
+      <c r="E189">
+        <v>449.9024968834</v>
+      </c>
+      <c r="F189">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2021/22</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>60 and over</t>
+        </is>
+      </c>
+      <c r="E190">
+        <v>89.17922051975</v>
+      </c>
+      <c r="F190">
+        <v>167.05</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2021/22</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Under 40</t>
+        </is>
+      </c>
+      <c r="E191">
+        <v>1177.286069275867</v>
+      </c>
+      <c r="F191">
+        <v>1812.733333333333</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2021/22</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E192">
+        <v>51.9563104199</v>
+      </c>
+      <c r="F192">
+        <v>87.2</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2021/22</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
+      </c>
+      <c r="E193">
+        <v>385.1248948088</v>
+      </c>
+      <c r="F193">
+        <v>539.3</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2021/22</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
+      </c>
+      <c r="E194">
+        <v>249.30951708925</v>
+      </c>
+      <c r="F194">
+        <v>367.05</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2021/22</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>60 and over</t>
+        </is>
+      </c>
+      <c r="E195">
+        <v>121.66199847725</v>
+      </c>
+      <c r="F195">
+        <v>201.75</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2021/22</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Under 40</t>
+        </is>
+      </c>
+      <c r="E196">
+        <v>477.9751538493333</v>
+      </c>
+      <c r="F196">
+        <v>664.2</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2021/22</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E197">
+        <v>32.8026864337</v>
+      </c>
+      <c r="F197">
+        <v>47.1</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2021/22</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
+      </c>
+      <c r="E198">
+        <v>1.45254258305</v>
+      </c>
+      <c r="F198">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2021/22</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
+      </c>
+      <c r="E199">
+        <v>1.346488888666667</v>
+      </c>
+      <c r="F199">
+        <v>2.333333333333333</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2021/22</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>60 and over</t>
+        </is>
+      </c>
+      <c r="E200">
+        <v>1.8786922651</v>
+      </c>
+      <c r="F200">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2021/22</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Under 40</t>
+        </is>
+      </c>
+      <c r="E201">
+        <v>3.996440685714286</v>
+      </c>
+      <c r="F201">
+        <v>5.666666666666667</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2021/22</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E202">
+        <v>72.8278255563</v>
+      </c>
+      <c r="F202">
+        <v>116.7</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2022/23</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
+      </c>
+      <c r="E203">
+        <v>1402.315989808458</v>
+      </c>
+      <c r="F203">
+        <v>1847.5</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2022/23</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
+      </c>
+      <c r="E204">
+        <v>1239.330065785083</v>
+      </c>
+      <c r="F204">
+        <v>1571.916666666667</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2022/23</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>60 and over</t>
+        </is>
+      </c>
+      <c r="E205">
+        <v>286.1105929470833</v>
+      </c>
+      <c r="F205">
+        <v>354.5</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2022/23</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Under 40</t>
+        </is>
+      </c>
+      <c r="E206">
+        <v>346.1494638096945</v>
+      </c>
+      <c r="F206">
+        <v>446.7777777777778</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2022/23</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E207">
+        <v>9.647615326583333</v>
+      </c>
+      <c r="F207">
+        <v>14.25</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2022/23</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
+      </c>
+      <c r="E208">
+        <v>1707.11138049175</v>
+      </c>
+      <c r="F208">
+        <v>1820.208333333333</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2022/23</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
+      </c>
+      <c r="E209">
+        <v>1712.273763038042</v>
+      </c>
+      <c r="F209">
+        <v>1801.875</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2022/23</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>60 and over</t>
+        </is>
+      </c>
+      <c r="E210">
+        <v>814.3415478000417</v>
+      </c>
+      <c r="F210">
+        <v>915.4166666666666</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2022/23</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Under 40</t>
+        </is>
+      </c>
+      <c r="E211">
+        <v>392.2059642673333</v>
+      </c>
+      <c r="F211">
+        <v>445.8055555555555</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2022/23</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E212">
+        <v>18.93176235908333</v>
+      </c>
+      <c r="F212">
+        <v>23.75</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2022/23</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
+      </c>
+      <c r="E213">
+        <v>2.533333334</v>
+      </c>
+      <c r="F213">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2022/23</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
+      </c>
+      <c r="E214">
+        <v>0.76</v>
+      </c>
+      <c r="F214">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2022/23</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E215">
+        <v>140.9796050905833</v>
+      </c>
+      <c r="F215">
+        <v>168.1666666666667</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2022/23</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
+      </c>
+      <c r="E216">
+        <v>1060.618832029833</v>
+      </c>
+      <c r="F216">
+        <v>1805.041666666667</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2022/23</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
+      </c>
+      <c r="E217">
+        <v>463.6580494384167</v>
+      </c>
+      <c r="F217">
+        <v>814.5416666666666</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2022/23</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>60 and over</t>
+        </is>
+      </c>
+      <c r="E218">
+        <v>98.05957321437499</v>
+      </c>
+      <c r="F218">
+        <v>181.1666666666667</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2022/23</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Under 40</t>
+        </is>
+      </c>
+      <c r="E219">
+        <v>1145.510920901417</v>
+      </c>
+      <c r="F219">
+        <v>1763.444444444444</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2022/23</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E220">
+        <v>42.88208620866667</v>
+      </c>
+      <c r="F220">
+        <v>71.25</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2022/23</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
+      </c>
+      <c r="E221">
+        <v>398.19636470025</v>
+      </c>
+      <c r="F221">
+        <v>558.2083333333334</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2022/23</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
+      </c>
+      <c r="E222">
+        <v>247.3894738316667</v>
+      </c>
+      <c r="F222">
+        <v>362.375</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2022/23</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>60 and over</t>
+        </is>
+      </c>
+      <c r="E223">
+        <v>124.6822430829583</v>
+      </c>
+      <c r="F223">
+        <v>217.5</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2022/23</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Under 40</t>
+        </is>
+      </c>
+      <c r="E224">
+        <v>478.5967939955833</v>
+      </c>
+      <c r="F224">
+        <v>667.9166666666666</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2022/23</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E225">
+        <v>28.1289066005</v>
+      </c>
+      <c r="F225">
+        <v>38.08333333333334</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2022/23</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
+      </c>
+      <c r="E226">
+        <v>1.568695652347826</v>
+      </c>
+      <c r="F226">
+        <v>2.608695652173913</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2022/23</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
+      </c>
+      <c r="E227">
+        <v>0.9436289852608696</v>
+      </c>
+      <c r="F227">
+        <v>1.782608695652174</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2022/23</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>60 and over</t>
+        </is>
+      </c>
+      <c r="E228">
+        <v>1.86</v>
+      </c>
+      <c r="F228">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2022/23</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Under 40</t>
+        </is>
+      </c>
+      <c r="E229">
+        <v>2.838274511958333</v>
+      </c>
+      <c r="F229">
+        <v>4.041666666666667</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2022/23</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E230">
+        <v>82.82302087533333</v>
+      </c>
+      <c r="F230">
+        <v>133.0833333333333</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2023/24</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
+      </c>
+      <c r="E231">
+        <v>1382.634272613917</v>
+      </c>
+      <c r="F231">
+        <v>1820.916666666667</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2023/24</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
+      </c>
+      <c r="E232">
+        <v>1237.86150958175</v>
+      </c>
+      <c r="F232">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2023/24</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>60 and over</t>
+        </is>
+      </c>
+      <c r="E233">
+        <v>301.4996127312083</v>
+      </c>
+      <c r="F233">
+        <v>374.375</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2023/24</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Under 40</t>
+        </is>
+      </c>
+      <c r="E234">
+        <v>328.4030823195833</v>
+      </c>
+      <c r="F234">
+        <v>427.6666666666667</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2023/24</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E235">
+        <v>8.209908423</v>
+      </c>
+      <c r="F235">
+        <v>11.91666666666667</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2023/24</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
+      </c>
+      <c r="E236">
+        <v>1635.238789439958</v>
+      </c>
+      <c r="F236">
+        <v>1757.5</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2023/24</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
+      </c>
+      <c r="E237">
+        <v>1653.089172898125</v>
+      </c>
+      <c r="F237">
+        <v>1738.458333333333</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2023/24</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>60 and over</t>
+        </is>
+      </c>
+      <c r="E238">
+        <v>813.3117012087083</v>
+      </c>
+      <c r="F238">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2023/24</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Under 40</t>
+        </is>
+      </c>
+      <c r="E239">
+        <v>374.7790156986667</v>
+      </c>
+      <c r="F239">
+        <v>426.8333333333333</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2023/24</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E240">
+        <v>15.50473199066667</v>
+      </c>
+      <c r="F240">
+        <v>19.25</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2023/24</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
+      </c>
+      <c r="E241">
+        <v>2.000000000666667</v>
+      </c>
+      <c r="F241">
+        <v>2.333333333333333</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2023/24</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
+      </c>
+      <c r="E242">
+        <v>0.76</v>
+      </c>
+      <c r="F242">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2023/24</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E243">
+        <v>140.3258464814167</v>
+      </c>
+      <c r="F243">
+        <v>167.5</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2023/24</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
+      </c>
+      <c r="E244">
+        <v>1124.374024507292</v>
+      </c>
+      <c r="F244">
+        <v>1920.75</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2023/24</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
+      </c>
+      <c r="E245">
+        <v>498.61582387025</v>
+      </c>
+      <c r="F245">
+        <v>877.9583333333334</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2023/24</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>60 and over</t>
+        </is>
+      </c>
+      <c r="E246">
+        <v>111.4508849037083</v>
+      </c>
+      <c r="F246">
+        <v>204.4166666666667</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2023/24</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Under 40</t>
+        </is>
+      </c>
+      <c r="E247">
+        <v>1126.110667752944</v>
+      </c>
+      <c r="F247">
+        <v>1752.222222222222</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2023/24</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E248">
+        <v>39.55119813391667</v>
+      </c>
+      <c r="F248">
+        <v>64.25</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2023/24</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
+      </c>
+      <c r="E249">
+        <v>420.8798032112917</v>
+      </c>
+      <c r="F249">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2023/24</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
+      </c>
+      <c r="E250">
+        <v>249.8524346694583</v>
+      </c>
+      <c r="F250">
+        <v>373.5416666666667</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2023/24</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>60 and over</t>
+        </is>
+      </c>
+      <c r="E251">
+        <v>132.5116587566667</v>
+      </c>
+      <c r="F251">
+        <v>231.4583333333333</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2023/24</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Under 40</t>
+        </is>
+      </c>
+      <c r="E252">
+        <v>502.0292355010833</v>
+      </c>
+      <c r="F252">
+        <v>710.4166666666666</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2023/24</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E253">
+        <v>25.83555788041667</v>
+      </c>
+      <c r="F253">
+        <v>35.91666666666666</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2023/24</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
+      </c>
+      <c r="E254">
+        <v>1.1233333335</v>
+      </c>
+      <c r="F254">
+        <v>1.875</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2023/24</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
+      </c>
+      <c r="E255">
+        <v>0.8583238091904761</v>
+      </c>
+      <c r="F255">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2023/24</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>60 and over</t>
+        </is>
+      </c>
+      <c r="E256">
+        <v>1.690769230846154</v>
+      </c>
+      <c r="F256">
+        <v>2.538461538461538</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2023/24</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Under 40</t>
+        </is>
+      </c>
+      <c r="E257">
+        <v>1.7433376005</v>
+      </c>
+      <c r="F257">
+        <v>2.708333333333333</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2023/24</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E258">
+        <v>87.21494785933334</v>
+      </c>
+      <c r="F258">
+        <v>141.4166666666667</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2024/25</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
+      </c>
+      <c r="E259">
+        <v>1339.481248061958</v>
+      </c>
+      <c r="F259">
+        <v>1775.625</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2024/25</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
+      </c>
+      <c r="E260">
+        <v>1244.258660423667</v>
+      </c>
+      <c r="F260">
+        <v>1567.458333333333</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2024/25</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>60 and over</t>
+        </is>
+      </c>
+      <c r="E261">
+        <v>326.41971565225</v>
+      </c>
+      <c r="F261">
+        <v>405.8333333333333</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2024/25</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Under 40</t>
+        </is>
+      </c>
+      <c r="E262">
+        <v>281.9282532537222</v>
+      </c>
+      <c r="F262">
+        <v>368.9444444444445</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2024/25</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E263">
+        <v>7.907318888666667</v>
+      </c>
+      <c r="F263">
+        <v>11.33333333333333</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2024/25</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
+      </c>
+      <c r="E264">
+        <v>1563.279443674208</v>
+      </c>
+      <c r="F264">
+        <v>1695.916666666667</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2024/25</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
+      </c>
+      <c r="E265">
+        <v>1609.196205865458</v>
+      </c>
+      <c r="F265">
+        <v>1697.208333333333</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2024/25</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>60 and over</t>
+        </is>
+      </c>
+      <c r="E266">
+        <v>833.0626867749584</v>
+      </c>
+      <c r="F266">
+        <v>919.9166666666666</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2024/25</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Under 40</t>
+        </is>
+      </c>
+      <c r="E267">
+        <v>336.8977083860556</v>
+      </c>
+      <c r="F267">
+        <v>391.3888888888889</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2024/25</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E268">
+        <v>13.9503335195</v>
+      </c>
+      <c r="F268">
+        <v>16.75</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2024/25</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
+      </c>
+      <c r="E269">
+        <v>1.733333334</v>
+      </c>
+      <c r="F269">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2024/25</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E270">
+        <v>125.78766284725</v>
+      </c>
+      <c r="F270">
+        <v>150.1666666666667</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2024/25</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
+      </c>
+      <c r="E271">
+        <v>1256.650641111958</v>
+      </c>
+      <c r="F271">
+        <v>2171.291666666667</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2024/25</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
+      </c>
+      <c r="E272">
+        <v>569.4373550905</v>
+      </c>
+      <c r="F272">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2024/25</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>60 and over</t>
+        </is>
+      </c>
+      <c r="E273">
+        <v>125.8113052802083</v>
+      </c>
+      <c r="F273">
+        <v>234.0833333333333</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2024/25</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Under 40</t>
+        </is>
+      </c>
+      <c r="E274">
+        <v>1183.505734522972</v>
+      </c>
+      <c r="F274">
+        <v>1868</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2024/25</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E275">
+        <v>33.56841742666667</v>
+      </c>
+      <c r="F275">
+        <v>55.08333333333334</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2024/25</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
+      </c>
+      <c r="E276">
+        <v>491.6191133314583</v>
+      </c>
+      <c r="F276">
+        <v>710.4583333333334</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2024/25</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
+      </c>
+      <c r="E277">
+        <v>273.2262285413333</v>
+      </c>
+      <c r="F277">
+        <v>407.75</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2024/25</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>60 and over</t>
+        </is>
+      </c>
+      <c r="E278">
+        <v>146.3909508316667</v>
+      </c>
+      <c r="F278">
+        <v>252.6666666666667</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2024/25</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Under 40</t>
+        </is>
+      </c>
+      <c r="E279">
+        <v>600.8094556213889</v>
+      </c>
+      <c r="F279">
+        <v>859.9166666666666</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2024/25</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E280">
+        <v>24.01656968816667</v>
+      </c>
+      <c r="F280">
+        <v>33.16666666666666</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2024/25</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
+      </c>
+      <c r="E281">
+        <v>1</v>
+      </c>
+      <c r="F281">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2024/25</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
+      </c>
+      <c r="E282">
+        <v>0.533333333</v>
+      </c>
+      <c r="F282">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2024/25</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>60 and over</t>
+        </is>
+      </c>
+      <c r="E283">
+        <v>0.9805128205384616</v>
+      </c>
+      <c r="F283">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2024/25</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Under 40</t>
+        </is>
+      </c>
+      <c r="E284">
+        <v>1.075834532041667</v>
+      </c>
+      <c r="F284">
+        <v>2.166666666666667</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2024/25</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E285">
+        <v>85.23321540541667</v>
+      </c>
+      <c r="F285">
+        <v>139.75</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
           <t>2025/26</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr">
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
+      </c>
+      <c r="E286">
+        <v>1310.59928369717</v>
+      </c>
+      <c r="F286">
+        <v>1748.25</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
+      </c>
+      <c r="E287">
+        <v>1238.832978757425</v>
+      </c>
+      <c r="F287">
+        <v>1568.55</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>60 and over</t>
+        </is>
+      </c>
+      <c r="E288">
+        <v>344.525556654435</v>
+      </c>
+      <c r="F288">
+        <v>426.7</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Under 40</t>
+        </is>
+      </c>
+      <c r="E289">
+        <v>237.6381774430233</v>
+      </c>
+      <c r="F289">
+        <v>312.5333333333334</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E290">
+        <v>6.02933333288</v>
+      </c>
+      <c r="F290">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
+      </c>
+      <c r="E291">
+        <v>1507.64945040624</v>
+      </c>
+      <c r="F291">
+        <v>1644.3</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
+      </c>
+      <c r="E292">
+        <v>1580.328352557355</v>
+      </c>
+      <c r="F292">
+        <v>1671.4</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>60 and over</t>
+        </is>
+      </c>
+      <c r="E293">
+        <v>833.013027404685</v>
+      </c>
+      <c r="F293">
+        <v>918.6</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Under 40</t>
+        </is>
+      </c>
+      <c r="E294">
+        <v>300.9733519358367</v>
+      </c>
+      <c r="F294">
+        <v>354.8</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E295">
+        <v>11.28793952771</v>
+      </c>
+      <c r="F295">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
         <is>
           <t>Other/Unknown</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr">
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
+      </c>
+      <c r="E296">
+        <v>0.9629629632</v>
+      </c>
+      <c r="F296">
+        <v>1.111111111111111</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>GP Partners</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="D165">
-        <v>173.83708643623</v>
-      </c>
-      <c r="E165">
-        <v>240.9</v>
+      <c r="E297">
+        <v>100.73762398184</v>
+      </c>
+      <c r="F297">
+        <v>120.2</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
+      </c>
+      <c r="E298">
+        <v>1406.76054828728</v>
+      </c>
+      <c r="F298">
+        <v>2443.45</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
+      </c>
+      <c r="E299">
+        <v>623.20243508869</v>
+      </c>
+      <c r="F299">
+        <v>1099.35</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>60 and over</t>
+        </is>
+      </c>
+      <c r="E300">
+        <v>142.38525898753</v>
+      </c>
+      <c r="F300">
+        <v>265.3</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Under 40</t>
+        </is>
+      </c>
+      <c r="E301">
+        <v>1226.653298991013</v>
+      </c>
+      <c r="F301">
+        <v>1949.566666666667</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E302">
+        <v>28.21759045165</v>
+      </c>
+      <c r="F302">
+        <v>43.8</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
+      </c>
+      <c r="E303">
+        <v>565.706598145055</v>
+      </c>
+      <c r="F303">
+        <v>823.35</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
+      </c>
+      <c r="E304">
+        <v>296.353477195865</v>
+      </c>
+      <c r="F304">
+        <v>438.95</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>60 and over</t>
+        </is>
+      </c>
+      <c r="E305">
+        <v>157.145085471665</v>
+      </c>
+      <c r="F305">
+        <v>268.8</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Under 40</t>
+        </is>
+      </c>
+      <c r="E306">
+        <v>682.7008131904834</v>
+      </c>
+      <c r="F306">
+        <v>981.7333333333333</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E307">
+        <v>22.17870227775</v>
+      </c>
+      <c r="F307">
+        <v>31.3</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>40-49</t>
+        </is>
+      </c>
+      <c r="E308">
+        <v>0.95666666664375</v>
+      </c>
+      <c r="F308">
+        <v>1.4375</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>50-59</t>
+        </is>
+      </c>
+      <c r="E309">
+        <v>0.40533333323</v>
+      </c>
+      <c r="F309">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>60 and over</t>
+        </is>
+      </c>
+      <c r="E310">
+        <v>1</v>
+      </c>
+      <c r="F310">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Under 40</t>
+        </is>
+      </c>
+      <c r="E311">
+        <v>0.6865533688518518</v>
+      </c>
+      <c r="F311">
+        <v>1.518518518518519</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Salaried GPs</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Other/Unknown</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E312">
+        <v>73.09946245438999</v>
+      </c>
+      <c r="F312">
+        <v>120.7</v>
       </c>
     </row>
   </sheetData>
